--- a/data/Escenarios_DCH/Costo_variable/Swap_variable_3estaciones_2C/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Costo_variable/Swap_variable_3estaciones_2C/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Costo_variable\Swap_fixed_3estaciones_2C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Costo_variable\Swap_variable_3estaciones_2C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80531B94-57CB-4BE3-A109-79C50DBE88E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E8BCC-6133-4760-9F2B-5E3C3C771E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="393">
   <si>
     <t>id</t>
   </si>
@@ -1150,9 +1150,6 @@
   </si>
   <si>
     <t>C0593</t>
-  </si>
-  <si>
-    <t>Profile_fixed</t>
   </si>
   <si>
     <t>station_name</t>
@@ -2217,7 +2214,7 @@
         <v>62</v>
       </c>
       <c r="AE1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2309,10 +2306,10 @@
         <v>37</v>
       </c>
       <c r="AD2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AE2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2323,10 +2320,10 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>52</v>
@@ -2418,10 +2415,10 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>52</v>
@@ -2513,10 +2510,10 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>52</v>
@@ -2608,10 +2605,10 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>52</v>
@@ -2704,10 +2701,10 @@
         <v>351</v>
       </c>
       <c r="C7" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>52</v>
@@ -2800,10 +2797,10 @@
         <v>352</v>
       </c>
       <c r="C8" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>52</v>
@@ -2896,10 +2893,10 @@
         <v>353</v>
       </c>
       <c r="C9" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>52</v>
@@ -2992,10 +2989,10 @@
         <v>354</v>
       </c>
       <c r="C10" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>52</v>
@@ -3088,10 +3085,10 @@
         <v>355</v>
       </c>
       <c r="C11" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>52</v>
@@ -3184,10 +3181,10 @@
         <v>356</v>
       </c>
       <c r="C12" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>52</v>
@@ -3280,10 +3277,10 @@
         <v>357</v>
       </c>
       <c r="C13" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>52</v>
@@ -3376,10 +3373,10 @@
         <v>358</v>
       </c>
       <c r="C14" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>52</v>
@@ -3487,25 +3484,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C1" t="s">
         <v>372</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>373</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>374</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>375</v>
       </c>
-      <c r="F1" t="s">
-        <v>376</v>
-      </c>
       <c r="G1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3516,7 +3513,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -3525,7 +3522,7 @@
         <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
@@ -3539,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C3">
         <v>215756</v>
@@ -3565,7 +3562,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C4">
         <v>215756</v>
@@ -3591,7 +3588,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C5">
         <v>215756</v>
@@ -3631,22 +3628,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" t="s">
         <v>380</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>381</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>382</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>383</v>
       </c>
-      <c r="F1" t="s">
-        <v>384</v>
-      </c>
       <c r="G1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>53</v>
@@ -3660,7 +3657,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
@@ -3672,7 +3669,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2" s="33" t="s">
         <v>4</v>
@@ -3683,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C3">
         <v>18669</v>
@@ -3701,7 +3698,7 @@
         <v>79000</v>
       </c>
       <c r="H3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
